--- a/workspace/framework_paper/edf/edf-25/edf-25_times_success.xlsx
+++ b/workspace/framework_paper/edf/edf-25/edf-25_times_success.xlsx
@@ -438,13 +438,13 @@
         <v>0.5</v>
       </c>
       <c r="B2" t="n">
-        <v>0.01030085004866123</v>
+        <v>0.01080446679145098</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02993443315848708</v>
+        <v>0.0271935884654522</v>
       </c>
       <c r="D2" t="n">
-        <v>7.330829051695764</v>
+        <v>0.01848845755681396</v>
       </c>
     </row>
     <row r="3">
@@ -452,13 +452,13 @@
         <v>0.5210526315789473</v>
       </c>
       <c r="B3" t="n">
-        <v>0.01130907654684658</v>
+        <v>0.01112048778062066</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03356355478987098</v>
+        <v>0.03204548183828592</v>
       </c>
       <c r="D3" t="n">
-        <v>7.907540046051144</v>
+        <v>0.1616352900024504</v>
       </c>
     </row>
     <row r="4">
@@ -466,13 +466,13 @@
         <v>0.5421052631578948</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01380098717830454</v>
+        <v>0.01262807384288559</v>
       </c>
       <c r="C4" t="n">
-        <v>0.04094134533777833</v>
+        <v>0.03916463673114776</v>
       </c>
       <c r="D4" t="n">
-        <v>9.524796094074846</v>
+        <v>0.1847511786222458</v>
       </c>
     </row>
     <row r="5">
@@ -480,13 +480,13 @@
         <v>0.5631578947368421</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01465985317675707</v>
+        <v>0.01406341668916866</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05590956483036279</v>
+        <v>0.05102823821827769</v>
       </c>
       <c r="D5" t="n">
-        <v>20.61693793038527</v>
+        <v>1.137900152858347</v>
       </c>
     </row>
     <row r="6">
@@ -494,13 +494,13 @@
         <v>0.5842105263157895</v>
       </c>
       <c r="B6" t="n">
-        <v>0.03039906380455131</v>
+        <v>0.02861048203245129</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1041874108463526</v>
+        <v>0.09786016073077917</v>
       </c>
       <c r="D6" t="n">
-        <v>24.07954651894777</v>
+        <v>6.97311979142949</v>
       </c>
     </row>
     <row r="7">
@@ -508,13 +508,13 @@
         <v>0.6052631578947368</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01905419573534367</v>
+        <v>0.01813427916576349</v>
       </c>
       <c r="C7" t="n">
-        <v>0.07006503082811832</v>
+        <v>0.06661228740549817</v>
       </c>
       <c r="D7" t="n">
-        <v>24.77610095511092</v>
+        <v>1.80423461260274</v>
       </c>
     </row>
     <row r="8">
@@ -522,13 +522,13 @@
         <v>0.6263157894736842</v>
       </c>
       <c r="B8" t="n">
-        <v>0.02389208427289637</v>
+        <v>0.02219707817520674</v>
       </c>
       <c r="C8" t="n">
-        <v>0.1289378552108395</v>
+        <v>0.1228664188208629</v>
       </c>
       <c r="D8" t="n">
-        <v>29.69367989084937</v>
+        <v>3.190379435044466</v>
       </c>
     </row>
     <row r="9">
@@ -536,13 +536,13 @@
         <v>0.6473684210526316</v>
       </c>
       <c r="B9" t="n">
-        <v>0.04136982349944966</v>
+        <v>0.04068104459771088</v>
       </c>
       <c r="C9" t="n">
-        <v>0.234835952441109</v>
+        <v>0.2334805562933709</v>
       </c>
       <c r="D9" t="n">
-        <v>41.0349266425423</v>
+        <v>10.56400448083878</v>
       </c>
     </row>
     <row r="10">
@@ -550,13 +550,13 @@
         <v>0.6684210526315789</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02765696463533319</v>
+        <v>0.02733827572172651</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2991114163564311</v>
+        <v>0.2964578180677361</v>
       </c>
       <c r="D10" t="n">
-        <v>43.20729755710911</v>
+        <v>22.51080200836683</v>
       </c>
     </row>
     <row r="11">
@@ -564,13 +564,13 @@
         <v>0.6894736842105263</v>
       </c>
       <c r="B11" t="n">
-        <v>0.05191934099420905</v>
+        <v>0.05166243556886911</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4481407098472118</v>
+        <v>0.4443674646317959</v>
       </c>
       <c r="D11" t="n">
-        <v>85.79190048049477</v>
+        <v>36.23188551135051</v>
       </c>
     </row>
     <row r="12">
@@ -578,13 +578,13 @@
         <v>0.7105263157894737</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03404932024960335</v>
+        <v>0.03427614371937055</v>
       </c>
       <c r="C12" t="n">
-        <v>0.3305641509316586</v>
+        <v>0.3252774758471383</v>
       </c>
       <c r="D12" t="n">
-        <v>82.83313226699829</v>
+        <v>51.90848736989904</v>
       </c>
     </row>
     <row r="13">
@@ -592,13 +592,13 @@
         <v>0.7315789473684211</v>
       </c>
       <c r="B13" t="n">
-        <v>0.06762424628767702</v>
+        <v>0.06711732492678696</v>
       </c>
       <c r="C13" t="n">
-        <v>1.207732282578945</v>
+        <v>1.189373373389244</v>
       </c>
       <c r="D13" t="n">
-        <v>84.16819712694954</v>
+        <v>110.2690837086202</v>
       </c>
     </row>
     <row r="14">
@@ -606,13 +606,13 @@
         <v>0.7526315789473684</v>
       </c>
       <c r="B14" t="n">
-        <v>0.04780584201216698</v>
+        <v>0.04709044173359871</v>
       </c>
       <c r="C14" t="n">
-        <v>6.471862497925758</v>
+        <v>6.341577684879303</v>
       </c>
       <c r="D14" t="n">
-        <v>115.3127509752909</v>
+        <v>117.044964191424</v>
       </c>
     </row>
     <row r="15">
@@ -620,13 +620,13 @@
         <v>0.7736842105263158</v>
       </c>
       <c r="B15" t="n">
-        <v>0.04530995960036913</v>
+        <v>0.04346955567598343</v>
       </c>
       <c r="C15" t="n">
-        <v>0.38217355446382</v>
+        <v>0.3780613033608957</v>
       </c>
       <c r="D15" t="n">
-        <v>145.0205738462251</v>
+        <v>147.4007948862655</v>
       </c>
     </row>
     <row r="16">
@@ -634,13 +634,13 @@
         <v>0.7947368421052632</v>
       </c>
       <c r="B16" t="n">
-        <v>0.06884599973758061</v>
+        <v>0.06856917962431908</v>
       </c>
       <c r="C16" t="n">
-        <v>3.209634080529213</v>
+        <v>3.190591897476803</v>
       </c>
       <c r="D16" t="n">
-        <v>136.0298228012888</v>
+        <v>269.7645608276913</v>
       </c>
     </row>
     <row r="17">
@@ -649,10 +649,10 @@
       </c>
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="n">
-        <v>0.934018949046731</v>
+        <v>0.9237382505089045</v>
       </c>
       <c r="D17" t="n">
-        <v>169.8141184720126</v>
+        <v>259.0782824605703</v>
       </c>
     </row>
     <row r="18">
@@ -661,10 +661,10 @@
       </c>
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="n">
-        <v>5.851586925131934</v>
+        <v>5.757320135831833</v>
       </c>
       <c r="D18" t="n">
-        <v>192.8889470100403</v>
+        <v>426.4682205200195</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>5.837221205234528</v>
+        <v>5.765368431806564</v>
       </c>
       <c r="D19" t="n">
-        <v>290.914465713501</v>
+        <v>396.4182159423828</v>
       </c>
     </row>
     <row r="20">
@@ -684,12 +684,8 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="n">
-        <v>22.81959772109985</v>
-      </c>
-      <c r="D20" t="n">
-        <v>597.375942993164</v>
-      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">

--- a/workspace/framework_paper/edf/edf-25/edf-25_times_success.xlsx
+++ b/workspace/framework_paper/edf/edf-25/edf-25_times_success.xlsx
@@ -673,10 +673,10 @@
       </c>
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="n">
-        <v>5.765368431806564</v>
+        <v>1.84499129652977</v>
       </c>
       <c r="D19" t="n">
-        <v>396.4182159423828</v>
+        <v>553.5008575439454</v>
       </c>
     </row>
     <row r="20">
@@ -684,8 +684,12 @@
         <v>0.8789473684210527</v>
       </c>
       <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>14.69113981723785</v>
+      </c>
+      <c r="D20" t="n">
+        <v>922.9582061767578</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -693,7 +697,9 @@
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="n">
+        <v>797.575927734375</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
